--- a/IB/5/График.xlsx
+++ b/IB/5/График.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Labs_6\IB\5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BCE882A-4708-4B56-A1A8-A4BA3A25991C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA36CCA4-989A-418F-B98B-0A98EB6FD048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AD64C877-A90B-4B34-A421-EB91A2C6ABEE}"/>
   </bookViews>
